--- a/gst_report.xlsx
+++ b/gst_report.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,69 +413,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Bill No</t>
+          <t>BILL</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>SUPPLIER</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Taxable</t>
+          <t>PRODUCT</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>PURCHASE PRICE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>TAXABLE</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>CGST</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SGST</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Total</t>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>IGST</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>TAX TYPE</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>46090.63337962963</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>01-04-2026</t>
+        </is>
       </c>
       <c r="B2" t="n">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAIZANN </t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4177.97</v>
+          <t>Khanna</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pipes - STEEL</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>376.02</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>376.02</v>
+        <v>320</v>
       </c>
       <c r="G2" t="n">
-        <v>4930</v>
+        <v>960</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24</v>
+      </c>
+      <c r="I2" t="n">
+        <v>24</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>INTRA</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1008</v>
       </c>
     </row>
   </sheetData>
